--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:16</t>
+    <t xml:space="preserve">2026-09-09 22:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:15</t>
+    <t xml:space="preserve">2026-09-17 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,18 +955,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11.56</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="4">
@@ -1015,68 +1015,68 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>12.27</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11.11</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12.09</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11.56</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11.41</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="8">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:41</t>
+    <t xml:space="preserve">2026-09-25 21:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -553,7 +553,7 @@
         <v>-1.22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-12.71</v>
+        <v>-12.68</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>5</v>
@@ -576,7 +576,7 @@
         <v>-0.97</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-8.58</v>
+        <v>-8.59</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -622,7 +622,7 @@
         <v>-0.39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3.87</v>
+        <v>-3.85</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>-0.53</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4.38</v>
+        <v>-4.36</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -691,7 +691,7 @@
         <v>-0.41</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4.07</v>
+        <v>-4.03</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>-0.65</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5.3</v>
+        <v>-5.28</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -760,7 +760,7 @@
         <v>-0.43</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4.13</v>
+        <v>-4.15</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -783,7 +783,7 @@
         <v>-0.6</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4.74</v>
+        <v>-4.76</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -803,10 +803,10 @@
         <v>18.1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-1</v>
+        <v>-0.99</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5.52</v>
+        <v>-5.47</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -829,7 +829,7 @@
         <v>-0.45</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4</v>
+        <v>-3.97</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
         <v>-0.65</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4.6</v>
+        <v>-4.59</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_los_lagos.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:40</t>
+    <t xml:space="preserve">2026-10-05 07:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
